--- a/StructureDefinition-SEEHDSImmunization.xlsx
+++ b/StructureDefinition-SEEHDSImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSImmunization.xlsx
+++ b/StructureDefinition-SEEHDSImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSImmunization.xlsx
+++ b/StructureDefinition-SEEHDSImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSImmunization.xlsx
+++ b/StructureDefinition-SEEHDSImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1554,7 +1554,7 @@
 </t>
   </si>
   <si>
-    <t>Ostrukturerad anteckning (registrationRecord.vaccinationUnstructuredNote) / kommentar</t>
+    <t>Anteckningar: vaccinationUnstructuredNote, kommentarer och dokumenttitel ("Dokumenttitel: …", VAC-004)</t>
   </si>
   <si>
     <t>Extra information about the immunization that is not conveyed by the other attributes.</t>

--- a/StructureDefinition-SEEHDSImmunization.xlsx
+++ b/StructureDefinition-SEEHDSImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSImmunization.xlsx
+++ b/StructureDefinition-SEEHDSImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSImmunization.xlsx
+++ b/StructureDefinition-SEEHDSImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSImmunization.xlsx
+++ b/StructureDefinition-SEEHDSImmunization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSImmunization.xlsx
+++ b/StructureDefinition-SEEHDSImmunization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$122</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4388" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4502" uniqueCount="616">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1169,6 +1169,15 @@
     <t>dateTime.value</t>
   </si>
   <si>
+    <t>Immunization.occurrence[x]:occurrenceString</t>
+  </si>
+  <si>
+    <t>occurrenceString</t>
+  </si>
+  <si>
+    <t>Vaccine administration date</t>
+  </si>
+  <si>
     <t>Immunization.recorded</t>
   </si>
   <si>
@@ -1373,6 +1382,10 @@
   </si>
   <si>
     <t>The quantity of vaccine product that was administered.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>RXA-6 / RXA-7</t>
@@ -1892,6 +1905,12 @@
     <t>Dosnummer (administrationRecord.doseOrdinalNumber)</t>
   </si>
   <si>
+    <t>Immunization.protocolApplied.doseNumber[x]:doseNumberString</t>
+  </si>
+  <si>
+    <t>doseNumberString</t>
+  </si>
+  <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
   </si>
   <si>
@@ -1908,6 +1927,12 @@
   </si>
   <si>
     <t>Antal ordinerade doser (administrationRecord.numberOfPrescribedDoses)</t>
+  </si>
+  <si>
+    <t>Immunization.protocolApplied.seriesDoses[x]:seriesDosesString</t>
+  </si>
+  <si>
+    <t>seriesDosesString</t>
   </si>
 </sst>
 </file>
@@ -2224,7 +2249,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO119"/>
+  <dimension ref="A1:AO122"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="66.5703125" customWidth="true" bestFit="true"/>
@@ -9011,14 +9036,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>370</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9030,24 +9057,26 @@
         <v>89</v>
       </c>
       <c r="H59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J59" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K59" t="s" s="2">
-        <v>342</v>
+        <v>103</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -9096,10 +9125,10 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>370</v>
+        <v>329</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>89</v>
@@ -9111,27 +9140,27 @@
         <v>101</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>78</v>
+        <v>335</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>78</v>
+        <v>336</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>373</v>
+        <v>337</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>374</v>
+        <v>338</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>78</v>
+        <v>339</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9151,20 +9180,18 @@
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9213,7 +9240,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9231,13 +9258,13 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>380</v>
+        <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -9245,10 +9272,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9268,19 +9295,19 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>220</v>
+        <v>379</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9306,13 +9333,13 @@
         <v>78</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>387</v>
+        <v>78</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>388</v>
+        <v>78</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>78</v>
@@ -9330,7 +9357,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9348,24 +9375,24 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9379,7 +9406,7 @@
         <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>78</v>
@@ -9388,15 +9415,17 @@
         <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>391</v>
+        <v>220</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
@@ -9421,13 +9450,13 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>78</v>
+        <v>391</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -9445,7 +9474,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9460,16 +9489,16 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>394</v>
+        <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>78</v>
@@ -9477,10 +9506,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9503,13 +9532,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9560,7 +9589,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9575,27 +9604,27 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>78</v>
+        <v>397</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9609,7 +9638,7 @@
         <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>78</v>
@@ -9618,13 +9647,13 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>103</v>
+        <v>402</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9675,7 +9704,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9693,24 +9722,24 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AM64" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>411</v>
-      </c>
       <c r="B65" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9724,7 +9753,7 @@
         <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>78</v>
@@ -9733,13 +9762,13 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>412</v>
+        <v>103</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9790,7 +9819,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9808,24 +9837,24 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>78</v>
+        <v>413</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9839,7 +9868,7 @@
         <v>89</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>78</v>
@@ -9848,13 +9877,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>220</v>
+        <v>415</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9881,13 +9910,13 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>421</v>
+        <v>78</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -9905,7 +9934,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9923,24 +9952,24 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>424</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9966,10 +9995,10 @@
         <v>220</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9999,10 +10028,10 @@
         <v>155</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -10020,7 +10049,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10038,24 +10067,24 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10078,13 +10107,13 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>434</v>
+        <v>220</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10111,13 +10140,13 @@
         <v>78</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>78</v>
+        <v>431</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>78</v>
+        <v>432</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -10135,7 +10164,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10153,24 +10182,24 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>78</v>
+        <v>435</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10181,25 +10210,25 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10238,38 +10267,40 @@
         <v>78</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AC69" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>440</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>444</v>
+        <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
@@ -10280,10 +10311,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10294,7 +10325,7 @@
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -10303,16 +10334,16 @@
         <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>103</v>
+        <v>444</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>104</v>
+        <v>445</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>105</v>
+        <v>446</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10351,40 +10382,38 @@
         <v>78</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>447</v>
+      </c>
+      <c r="AC70" s="2"/>
       <c r="AD70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>106</v>
+        <v>443</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>78</v>
+        <v>448</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>78</v>
+        <v>449</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>107</v>
+        <v>450</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -10395,21 +10424,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
@@ -10421,17 +10450,15 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10480,19 +10507,19 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>78</v>
@@ -10512,14 +10539,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>450</v>
+        <v>109</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10532,26 +10559,24 @@
         <v>78</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>451</v>
+        <v>111</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>452</v>
+        <v>112</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O72" t="s" s="2">
-        <v>275</v>
-      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10599,7 +10624,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>453</v>
+        <v>117</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10620,7 +10645,7 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10631,33 +10656,33 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>78</v>
+        <v>454</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>455</v>
@@ -10665,8 +10690,12 @@
       <c r="M73" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+      <c r="N73" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10690,52 +10719,52 @@
         <v>78</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>459</v>
+        <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>460</v>
+        <v>188</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10746,10 +10775,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10757,7 +10786,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>89</v>
@@ -10772,17 +10801,15 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>462</v>
+        <v>220</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10807,13 +10834,13 @@
         <v>78</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>78</v>
+        <v>461</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>78</v>
+        <v>462</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
@@ -10831,10 +10858,10 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>89</v>
@@ -10846,43 +10873,41 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>468</v>
+        <v>78</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>78</v>
@@ -10891,15 +10916,17 @@
         <v>90</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10948,13 +10975,13 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>78</v>
@@ -10963,29 +10990,31 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>445</v>
+        <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>78</v>
+        <v>472</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C76" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="D76" t="s" s="2">
         <v>78</v>
       </c>
@@ -10994,25 +11023,25 @@
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>103</v>
+        <v>444</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>104</v>
+        <v>475</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>105</v>
+        <v>446</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11063,28 +11092,28 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>106</v>
+        <v>443</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>78</v>
+        <v>448</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>78</v>
+        <v>449</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>107</v>
+        <v>450</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>78</v>
@@ -11095,21 +11124,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
@@ -11121,17 +11150,15 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -11180,19 +11207,19 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
@@ -11212,14 +11239,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>450</v>
+        <v>109</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11232,26 +11259,24 @@
         <v>78</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>451</v>
+        <v>111</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>452</v>
+        <v>112</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O78" t="s" s="2">
-        <v>275</v>
-      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>78</v>
       </c>
@@ -11299,7 +11324,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>453</v>
+        <v>117</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11320,7 +11345,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -11331,33 +11356,33 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>78</v>
+        <v>454</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J79" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>455</v>
@@ -11365,8 +11390,12 @@
       <c r="M79" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+      <c r="N79" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
       </c>
@@ -11375,7 +11404,7 @@
         <v>78</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>476</v>
+        <v>78</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>78</v>
@@ -11390,66 +11419,66 @@
         <v>78</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="Y79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF79" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="Z79" t="s" s="2">
+      <c r="AG79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B80" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11457,13 +11486,13 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>78</v>
@@ -11472,17 +11501,15 @@
         <v>90</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>478</v>
+        <v>220</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -11492,7 +11519,7 @@
         <v>78</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>78</v>
+        <v>480</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>78</v>
@@ -11507,13 +11534,13 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>78</v>
+        <v>461</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>78</v>
+        <v>462</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11531,10 +11558,10 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>89</v>
@@ -11546,16 +11573,16 @@
         <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>468</v>
+        <v>78</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>78</v>
@@ -11563,20 +11590,18 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C81" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>89</v>
@@ -11591,15 +11616,17 @@
         <v>90</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>440</v>
+        <v>482</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>441</v>
+        <v>483</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>78</v>
@@ -11648,13 +11675,13 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>78</v>
@@ -11663,29 +11690,31 @@
         <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>445</v>
+        <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>78</v>
+        <v>472</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C82" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="D82" t="s" s="2">
         <v>78</v>
       </c>
@@ -11697,22 +11726,22 @@
         <v>89</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>103</v>
+        <v>444</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>104</v>
+        <v>445</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>105</v>
+        <v>446</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11763,28 +11792,28 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>106</v>
+        <v>443</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>78</v>
+        <v>448</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>78</v>
+        <v>449</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>107</v>
+        <v>450</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11795,21 +11824,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
@@ -11821,17 +11850,15 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -11880,19 +11907,19 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
@@ -11912,14 +11939,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>450</v>
+        <v>109</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11932,26 +11959,24 @@
         <v>78</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>451</v>
+        <v>111</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>452</v>
+        <v>112</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O84" t="s" s="2">
-        <v>275</v>
-      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>78</v>
       </c>
@@ -11999,7 +12024,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>453</v>
+        <v>117</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12020,7 +12045,7 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -12029,35 +12054,35 @@
         <v>78</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>78</v>
+        <v>454</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I85" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="J85" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>455</v>
@@ -12065,8 +12090,12 @@
       <c r="M85" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+      <c r="N85" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12075,7 +12104,7 @@
         <v>78</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>486</v>
+        <v>78</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>78</v>
@@ -12090,52 +12119,52 @@
         <v>78</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="Z85" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>454</v>
-      </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>459</v>
+        <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>460</v>
+        <v>188</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -12146,10 +12175,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12157,7 +12186,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>89</v>
@@ -12172,17 +12201,15 @@
         <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>478</v>
+        <v>220</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>488</v>
+        <v>459</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -12192,7 +12219,7 @@
         <v>78</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>78</v>
+        <v>490</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>78</v>
@@ -12207,13 +12234,13 @@
         <v>78</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>78</v>
+        <v>461</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>78</v>
+        <v>462</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>78</v>
@@ -12231,10 +12258,10 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>89</v>
@@ -12246,16 +12273,16 @@
         <v>101</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>468</v>
+        <v>78</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>78</v>
@@ -12263,10 +12290,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>489</v>
+        <v>465</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12274,10 +12301,10 @@
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>90</v>
@@ -12289,15 +12316,17 @@
         <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>78</v>
@@ -12346,13 +12375,13 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>489</v>
+        <v>465</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>78</v>
@@ -12361,27 +12390,27 @@
         <v>101</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AL87" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>496</v>
-      </c>
       <c r="B88" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12395,22 +12424,22 @@
         <v>80</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>220</v>
+        <v>494</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12437,13 +12466,13 @@
         <v>78</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>499</v>
+        <v>78</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>500</v>
+        <v>78</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>78</v>
@@ -12461,7 +12490,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12476,13 +12505,13 @@
         <v>101</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>78</v>
+        <v>498</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>78</v>
@@ -12493,10 +12522,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12519,13 +12548,13 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>504</v>
+        <v>220</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12552,13 +12581,13 @@
         <v>78</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>78</v>
+        <v>503</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>78</v>
+        <v>504</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>78</v>
@@ -12576,7 +12605,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12591,13 +12620,13 @@
         <v>101</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>188</v>
+        <v>506</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>78</v>
@@ -12608,10 +12637,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12622,19 +12651,19 @@
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>376</v>
+        <v>508</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>509</v>
@@ -12642,16 +12671,12 @@
       <c r="M90" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="N90" t="s" s="2">
-        <v>511</v>
-      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q90" t="s" s="2">
-        <v>512</v>
-      </c>
+      <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
         <v>78</v>
       </c>
@@ -12695,13 +12720,13 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>78</v>
@@ -12710,10 +12735,10 @@
         <v>101</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>78</v>
+        <v>511</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>513</v>
+        <v>78</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>188</v>
@@ -12727,10 +12752,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12741,32 +12766,36 @@
         <v>79</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>220</v>
+        <v>379</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M91" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q91" s="2"/>
+      <c r="Q91" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="R91" t="s" s="2">
         <v>78</v>
       </c>
@@ -12786,13 +12815,13 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>517</v>
+        <v>78</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>518</v>
+        <v>78</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -12810,13 +12839,13 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>78</v>
@@ -12828,7 +12857,7 @@
         <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>78</v>
+        <v>517</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>188</v>
@@ -12842,10 +12871,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12868,13 +12897,13 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>440</v>
+        <v>220</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12901,13 +12930,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>78</v>
+        <v>521</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -12925,7 +12954,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12937,7 +12966,7 @@
         <v>78</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>522</v>
+        <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>78</v>
@@ -12971,7 +13000,7 @@
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>78</v>
@@ -12983,13 +13012,13 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>103</v>
+        <v>444</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>104</v>
+        <v>524</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>105</v>
+        <v>525</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13040,19 +13069,19 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>106</v>
+        <v>523</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>78</v>
+        <v>526</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>78</v>
@@ -13061,7 +13090,7 @@
         <v>78</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>107</v>
+        <v>188</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -13072,21 +13101,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
@@ -13098,17 +13127,15 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>78</v>
@@ -13157,19 +13184,19 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>78</v>
@@ -13189,14 +13216,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>450</v>
+        <v>109</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13209,26 +13236,24 @@
         <v>78</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>451</v>
+        <v>111</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>452</v>
+        <v>112</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O95" t="s" s="2">
-        <v>275</v>
-      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>78</v>
       </c>
@@ -13276,7 +13301,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>453</v>
+        <v>117</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13297,7 +13322,7 @@
         <v>78</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -13308,42 +13333,46 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>78</v>
+        <v>454</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>527</v>
+        <v>455</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
@@ -13391,25 +13420,25 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>526</v>
+        <v>457</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>529</v>
+        <v>78</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>188</v>
@@ -13449,7 +13478,7 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="L97" t="s" s="2">
         <v>531</v>
@@ -13524,7 +13553,7 @@
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>188</v>
@@ -13538,10 +13567,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13564,13 +13593,13 @@
         <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>342</v>
+        <v>131</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13621,7 +13650,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13639,7 +13668,7 @@
         <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>536</v>
+        <v>78</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>188</v>
@@ -13766,7 +13795,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
         <v>541</v>
       </c>
@@ -13782,10 +13811,10 @@
         <v>79</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>78</v>
@@ -13794,7 +13823,7 @@
         <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>220</v>
+        <v>342</v>
       </c>
       <c r="L100" t="s" s="2">
         <v>542</v>
@@ -13827,13 +13856,13 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>544</v>
+        <v>78</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>545</v>
+        <v>78</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -13857,7 +13886,7 @@
         <v>79</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>78</v>
@@ -13869,7 +13898,7 @@
         <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>188</v>
@@ -13881,12 +13910,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13897,10 +13926,10 @@
         <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>78</v>
@@ -13912,10 +13941,10 @@
         <v>220</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13945,10 +13974,10 @@
         <v>155</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -13966,13 +13995,13 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>78</v>
@@ -13984,7 +14013,7 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>78</v>
+        <v>550</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>188</v>
@@ -13996,12 +14025,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14012,10 +14041,10 @@
         <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>78</v>
@@ -14024,17 +14053,15 @@
         <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>440</v>
+        <v>220</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M102" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>555</v>
-      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -14059,13 +14086,13 @@
         <v>78</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>78</v>
+        <v>554</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>78</v>
+        <v>555</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>78</v>
@@ -14083,13 +14110,13 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>78</v>
@@ -14101,24 +14128,24 @@
         <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AM102" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>558</v>
-      </c>
       <c r="B103" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14129,10 +14156,10 @@
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>78</v>
@@ -14141,15 +14168,17 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>103</v>
+        <v>444</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>104</v>
+        <v>557</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>558</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>559</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14198,28 +14227,28 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>106</v>
+        <v>556</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>78</v>
+        <v>560</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>107</v>
+        <v>561</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>78</v>
@@ -14230,21 +14259,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>78</v>
@@ -14256,17 +14285,15 @@
         <v>78</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -14315,19 +14342,19 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>78</v>
@@ -14347,14 +14374,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>450</v>
+        <v>109</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -14367,26 +14394,24 @@
         <v>78</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>451</v>
+        <v>111</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>452</v>
+        <v>112</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O105" t="s" s="2">
-        <v>275</v>
-      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>78</v>
       </c>
@@ -14434,7 +14459,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>453</v>
+        <v>117</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14455,7 +14480,7 @@
         <v>78</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>78</v>
@@ -14466,42 +14491,46 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>78</v>
+        <v>454</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>342</v>
+        <v>110</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>562</v>
+        <v>455</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>78</v>
       </c>
@@ -14549,28 +14578,28 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>561</v>
+        <v>457</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>564</v>
+        <v>78</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>337</v>
+        <v>188</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>78</v>
@@ -14607,13 +14636,13 @@
         <v>78</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L107" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="L107" t="s" s="2">
+      <c r="M107" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14682,10 +14711,10 @@
         <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>570</v>
+        <v>337</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>78</v>
@@ -14696,10 +14725,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14722,13 +14751,13 @@
         <v>78</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>376</v>
+        <v>570</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14779,7 +14808,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14797,24 +14826,24 @@
         <v>78</v>
       </c>
       <c r="AL108" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AM108" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="AM108" t="s" s="2">
+      <c r="AN108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="AN108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="B109" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14825,10 +14854,10 @@
         <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>78</v>
@@ -14837,13 +14866,13 @@
         <v>78</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>440</v>
+        <v>379</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14894,13 +14923,13 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>78</v>
@@ -14912,10 +14941,10 @@
         <v>78</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>78</v>
+        <v>578</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>188</v>
+        <v>579</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>78</v>
@@ -14924,12 +14953,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14940,10 +14969,10 @@
         <v>79</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>78</v>
@@ -14952,13 +14981,13 @@
         <v>78</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>103</v>
+        <v>444</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>104</v>
+        <v>581</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>105</v>
+        <v>582</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15009,19 +15038,19 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>106</v>
+        <v>580</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>78</v>
@@ -15030,7 +15059,7 @@
         <v>78</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>107</v>
+        <v>188</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>78</v>
@@ -15041,21 +15070,21 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>78</v>
@@ -15067,17 +15096,15 @@
         <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -15126,19 +15153,19 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>78</v>
@@ -15158,14 +15185,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>450</v>
+        <v>109</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15178,26 +15205,24 @@
         <v>78</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>451</v>
+        <v>111</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>452</v>
+        <v>112</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O112" t="s" s="2">
-        <v>275</v>
-      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>78</v>
       </c>
@@ -15245,7 +15270,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>453</v>
+        <v>117</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15266,7 +15291,7 @@
         <v>78</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>188</v>
+        <v>107</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>78</v>
@@ -15275,44 +15300,48 @@
         <v>78</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>78</v>
+        <v>454</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I113" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I113" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J113" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>583</v>
+        <v>455</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>78</v>
       </c>
@@ -15360,19 +15389,19 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>582</v>
+        <v>457</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>78</v>
@@ -15390,12 +15419,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15409,7 +15438,7 @@
         <v>89</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>78</v>
@@ -15418,13 +15447,13 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>399</v>
+        <v>103</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15475,7 +15504,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15505,12 +15534,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15521,10 +15550,10 @@
         <v>79</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>78</v>
@@ -15533,13 +15562,13 @@
         <v>78</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>220</v>
+        <v>402</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15566,13 +15595,13 @@
         <v>78</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>591</v>
+        <v>78</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>592</v>
+        <v>78</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>78</v>
@@ -15590,13 +15619,13 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>78</v>
@@ -15620,12 +15649,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="116" hidden="true">
+    <row r="116">
       <c r="A116" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15633,13 +15662,13 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>78</v>
@@ -15648,17 +15677,15 @@
         <v>78</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="L116" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>597</v>
-      </c>
+      <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -15683,35 +15710,37 @@
         <v>78</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>78</v>
+        <v>169</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>78</v>
+        <v>595</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>78</v>
+        <v>596</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AC116" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>78</v>
@@ -15735,28 +15764,26 @@
         <v>78</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>599</v>
-      </c>
+        <v>597</v>
+      </c>
+      <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G117" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>78</v>
@@ -15765,16 +15792,16 @@
         <v>78</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="N117" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15812,19 +15839,17 @@
         <v>78</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="AC117" s="2"/>
       <c r="AD117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>78</v>
+        <v>203</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>89</v>
@@ -15854,14 +15879,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
         <v>602</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C118" s="2"/>
+        <v>597</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>603</v>
+      </c>
       <c r="D118" t="s" s="2">
         <v>78</v>
       </c>
@@ -15873,7 +15900,7 @@
         <v>89</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>78</v>
@@ -15882,16 +15909,16 @@
         <v>78</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>594</v>
+        <v>604</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15929,20 +15956,22 @@
         <v>78</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AC118" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>89</v>
@@ -15969,15 +15998,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>78</v>
@@ -15990,7 +16019,7 @@
         <v>89</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>78</v>
@@ -15999,16 +16028,16 @@
         <v>78</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="L119" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>604</v>
-      </c>
       <c r="N119" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16058,10 +16087,10 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>89</v>
@@ -16088,8 +16117,361 @@
         <v>78</v>
       </c>
     </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AC120" s="2"/>
+      <c r="AD120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="D121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="D122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AO119">
+  <autoFilter ref="A1:AO122">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16099,7 +16481,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI118">
+  <conditionalFormatting sqref="A2:AI121">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
